--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -188,10 +188,10 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -944,19 +944,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -980,19 +980,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1021,19 +1021,19 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1060,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1098,19 +1098,19 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1134,10 +1134,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1175,19 +1175,19 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1214,16 +1214,16 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1252,19 +1252,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1288,19 +1288,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1329,19 +1329,19 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1365,13 +1365,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1406,19 +1406,19 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1448,13 +1448,13 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1483,19 +1483,19 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1522,16 +1522,16 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1563,16 +1563,16 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1637,19 +1637,19 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1714,19 +1714,19 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1750,19 +1750,19 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>6</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1791,19 +1791,19 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1827,19 +1827,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>5</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1868,19 +1868,19 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1904,19 +1904,19 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1945,19 +1945,19 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1984,16 +1984,16 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2022,19 +2022,19 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2058,19 +2058,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>5</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2099,19 +2099,19 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2135,19 +2135,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2176,19 +2176,19 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2215,16 +2215,16 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2253,19 +2253,19 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2289,13 +2289,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2330,19 +2330,19 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2372,13 +2372,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2407,19 +2407,19 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2443,19 +2443,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2484,19 +2484,19 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2520,19 +2520,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2561,19 +2561,19 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2606,10 +2606,10 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2638,19 +2638,19 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2674,19 +2674,19 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2715,19 +2715,19 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2751,13 +2751,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2792,19 +2792,19 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2828,7 +2828,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2837,10 +2837,10 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2869,19 +2869,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2908,16 +2908,16 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2946,19 +2946,19 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2985,16 +2985,16 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>10</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3023,19 +3023,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3059,7 +3059,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3136,13 +3136,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3177,19 +3177,19 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3213,13 +3213,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>6</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3254,19 +3254,19 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3290,7 +3290,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3331,19 +3331,19 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3370,16 +3370,16 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>10</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3447,19 +3447,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>78.13</v>
+        <v>68.75</v>
       </c>
       <c r="G2">
-        <v>21.88</v>
+        <v>31.25</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3479,19 +3479,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="G3">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>18.75</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3543,19 +3543,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G5">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3575,19 +3575,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4244,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920157</v>
+        <v>21330051920154</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920157</v>
+        <v>21330051920154</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4322,16 +4322,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920159</v>
+        <v>21330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4345,16 +4345,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920159</v>
+        <v>21330051920157</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920171</v>
+        <v>21330051920164</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4391,22 +4391,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920171</v>
+        <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4414,16 +4414,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920177</v>
+        <v>21330051920171</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4437,16 +4437,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920177</v>
+        <v>21330051920171</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -4460,16 +4460,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920181</v>
+        <v>21330051920177</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4483,16 +4483,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920181</v>
+        <v>21330051920177</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4506,16 +4506,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920153</v>
+        <v>21330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4529,22 +4529,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920165</v>
+        <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4552,16 +4552,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920175</v>
+        <v>21330051920176</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4570,6 +4570,29 @@
         <v>54</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -188,10 +188,10 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1560,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1596,7 +1596,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3575,19 +3575,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -959,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1036,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1113,7 +1113,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1149,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1190,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1226,7 +1226,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1267,7 +1267,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1303,7 +1303,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1344,7 +1344,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1421,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1498,7 +1498,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1575,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1652,7 +1652,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1806,7 +1806,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1842,7 +1842,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1883,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1960,7 +1960,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2037,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2073,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,7 +2114,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2191,7 +2191,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2227,7 +2227,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2268,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2304,7 +2304,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2422,7 +2422,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2458,7 +2458,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2535,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2576,7 +2576,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2653,7 +2653,7 @@
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2730,7 +2730,7 @@
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2807,7 +2807,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2843,7 +2843,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2884,7 +2884,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2961,7 +2961,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3038,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3115,7 +3115,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3151,7 +3151,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3192,7 +3192,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3228,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3269,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3346,7 +3346,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3382,7 +3382,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -182,10 +182,10 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
@@ -968,7 +968,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1045,7 +1045,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1122,7 +1122,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1199,7 +1199,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1276,7 +1276,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1353,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1430,7 +1430,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1507,7 +1507,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1584,7 +1584,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1661,7 +1661,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1738,7 +1738,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1815,7 +1815,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1969,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2046,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2123,7 +2123,7 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2372,7 +2372,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2431,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2508,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2585,7 +2585,7 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2662,7 +2662,7 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2739,7 +2739,7 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2816,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2893,7 +2893,7 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2970,7 +2970,7 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3047,7 +3047,7 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3124,7 +3124,7 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3201,7 +3201,7 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3278,7 +3278,7 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3355,7 +3355,7 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3373,7 +3373,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3491,7 +3491,7 @@
         <v>18.75</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3502,28 +3502,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>32</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G4">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3543,19 +3543,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4244,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4314,7 +4314,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4337,7 +4337,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4360,7 +4360,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4406,7 +4406,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4414,16 +4414,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920171</v>
+        <v>21330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920171</v>
+        <v>21330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4460,16 +4460,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920177</v>
+        <v>21330051920171</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4495,10 +4495,10 @@
         <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4506,16 +4506,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920152</v>
+        <v>21330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4524,75 +4524,6 @@
         <v>53</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920162</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920176</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920181</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -185,10 +185,10 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1039,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1134,7 +1134,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1193,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1211,7 +1211,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1270,7 +1270,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1424,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1578,7 +1578,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1655,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1732,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1750,7 +1750,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1809,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1827,7 +1827,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1886,7 +1886,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1904,7 +1904,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1963,7 +1963,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2040,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2058,7 +2058,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2117,7 +2117,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2194,7 +2194,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2271,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2289,7 +2289,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2348,7 +2348,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2366,7 +2366,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2425,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2520,7 +2520,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2579,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2597,7 +2597,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2733,7 +2733,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2751,7 +2751,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2810,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2887,7 +2887,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2964,7 +2964,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3041,7 +3041,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3118,7 +3118,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3195,7 +3195,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3349,7 +3349,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>32</v>
@@ -3523,7 +3523,7 @@
         <v>15.63</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3534,28 +3534,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>84.38</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>15.63</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3575,19 +3575,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>96.88</v>
+        <v>87.5</v>
       </c>
       <c r="G6">
-        <v>3.13</v>
+        <v>12.5</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4244,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920154</v>
+        <v>21330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920154</v>
+        <v>21330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4345,22 +4345,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4437,16 +4437,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920162</v>
+        <v>21330051920171</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4460,16 +4460,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920171</v>
+        <v>21330051920177</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4483,16 +4483,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920177</v>
+        <v>21330051920181</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4501,29 +4501,6 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920181</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -182,16 +182,16 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -965,16 +965,16 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -983,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1042,16 +1042,16 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1060,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1119,16 +1119,16 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1196,16 +1196,16 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1220,10 +1220,10 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1273,16 +1273,16 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1350,16 +1350,16 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1368,16 +1368,16 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1427,16 +1427,16 @@
         <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1445,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1504,16 +1504,16 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1522,16 +1522,16 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1581,16 +1581,16 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1599,16 +1599,16 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1658,16 +1658,16 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1676,7 +1676,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1735,16 +1735,16 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1759,10 +1759,10 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1836,10 +1836,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1889,16 +1889,16 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1966,16 +1966,16 @@
         <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1990,10 +1990,10 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2043,16 +2043,16 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2067,10 +2067,10 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2144,10 +2144,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2197,16 +2197,16 @@
         <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2221,10 +2221,10 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2274,16 +2274,16 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2298,10 +2298,10 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2351,16 +2351,16 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2375,10 +2375,10 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2428,16 +2428,16 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2505,16 +2505,16 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2529,10 +2529,10 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2582,16 +2582,16 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2659,16 +2659,16 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2736,16 +2736,16 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2754,16 +2754,16 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2813,16 +2813,16 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2831,16 +2831,16 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2890,16 +2890,16 @@
         <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2908,7 +2908,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2967,16 +2967,16 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3044,16 +3044,16 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3121,16 +3121,16 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3198,16 +3198,16 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3222,10 +3222,10 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3275,16 +3275,16 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3352,16 +3352,16 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3370,7 +3370,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3447,19 +3447,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="G2">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3479,19 +3479,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3511,19 +3511,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3534,28 +3534,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3566,28 +3566,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4244,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4276,19 +4276,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4345,22 +4345,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4391,22 +4391,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4437,16 +4437,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920171</v>
+        <v>21330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4460,16 +4460,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920177</v>
+        <v>21330051920157</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4483,16 +4483,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920181</v>
+        <v>21330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4501,6 +4501,52 @@
         <v>53</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920171</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920181</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20221.xlsx
+++ b/grupos/3AEM - Estadisticos 20221.xlsx
@@ -977,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1054,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1131,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1208,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1285,7 +1285,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1362,7 +1362,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1380,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1439,7 +1439,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1593,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1670,7 +1670,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1747,7 +1747,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1824,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1919,7 +1919,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1978,7 +1978,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2055,7 +2055,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2132,7 +2132,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2150,7 +2150,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2209,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2286,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2304,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2363,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2440,7 +2440,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2517,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2535,7 +2535,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2594,7 +2594,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2748,7 +2748,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2825,7 +2825,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2843,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2902,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2920,7 +2920,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2979,7 +2979,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3056,7 +3056,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3074,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3133,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3210,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3228,7 +3228,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3287,7 +3287,7 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3364,7 +3364,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
